--- a/ExportExcel/Update Academic Degrees Test.xlsx
+++ b/ExportExcel/Update Academic Degrees Test.xlsx
@@ -41,7 +41,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>4787 ms</t>
+    <t>4568 ms</t>
   </si>
   <si>
     <t/>
@@ -53,7 +53,7 @@
     <t>TC_UpdateADM_02</t>
   </si>
   <si>
-    <t>4468 ms</t>
+    <t>4438 ms</t>
   </si>
   <si>
     <t>testInvalidUpdateNameExceeds100Chars</t>
@@ -62,7 +62,7 @@
     <t>TC_UpdateADM_03</t>
   </si>
   <si>
-    <t>4418 ms</t>
+    <t>4759 ms</t>
   </si>
   <si>
     <t>testInvalidUpdateOrderEmpty</t>
@@ -71,7 +71,7 @@
     <t>TC_UpdateADM_04</t>
   </si>
   <si>
-    <t>4294 ms</t>
+    <t>4365 ms</t>
   </si>
   <si>
     <t>testInvalidUpdateOrderExceeds100</t>
@@ -80,7 +80,7 @@
     <t>TC_UpdateADM_05</t>
   </si>
   <si>
-    <t>4273 ms</t>
+    <t>4470 ms</t>
   </si>
   <si>
     <t>testInvalidUpdateOrderEqualsZero</t>
@@ -89,7 +89,7 @@
     <t>TC_UpdateADM_06</t>
   </si>
   <si>
-    <t>4235 ms</t>
+    <t>4266 ms</t>
   </si>
 </sst>
 </file>
